--- a/APPT/data/output/Final_Production_Plan_2026-01-19.xlsx
+++ b/APPT/data/output/Final_Production_Plan_2026-01-19.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1105" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="241">
   <si>
     <t>Production Line</t>
   </si>
@@ -130,22 +130,22 @@
     <t>H&amp;S Anti dandruff  7in1</t>
   </si>
   <si>
-    <t>CI606</t>
-  </si>
-  <si>
-    <t>CI608</t>
-  </si>
-  <si>
-    <t>CI609</t>
-  </si>
-  <si>
-    <t>CI604</t>
-  </si>
-  <si>
-    <t>CI605</t>
-  </si>
-  <si>
-    <t>CI607</t>
+    <t>CI619</t>
+  </si>
+  <si>
+    <t>CI621</t>
+  </si>
+  <si>
+    <t>CI622</t>
+  </si>
+  <si>
+    <t>CI617</t>
+  </si>
+  <si>
+    <t>CI618</t>
+  </si>
+  <si>
+    <t>CI620</t>
   </si>
   <si>
     <t>21448509</t>
@@ -184,19 +184,19 @@
     <t>B</t>
   </si>
   <si>
-    <t>TK#_24_# [Wash 20m] + TK#_22_# [Wash 20m]</t>
-  </si>
-  <si>
-    <t>TK#_13_# + TK#_5_#</t>
-  </si>
-  <si>
-    <t>TK#_26_# [Wash 20m]</t>
-  </si>
-  <si>
-    <t>TK#_10_#</t>
-  </si>
-  <si>
-    <t>TK#_1_# [Wash 20m]</t>
+    <t>TK#_17_# [Wash 20m] + TK#_5_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_20_# + TK#_16_#</t>
+  </si>
+  <si>
+    <t>TK#_11_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_7_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_24_# [Wash 20m]</t>
   </si>
   <si>
     <t>LOW: SLS</t>
@@ -607,48 +607,51 @@
     <t>C</t>
   </si>
   <si>
-    <t>CI606: H&amp;S Neem Libra</t>
+    <t>CI619: H&amp;S Neem Libra</t>
   </si>
   <si>
     <t>WASHOUT</t>
   </si>
   <si>
-    <t>CI608: H&amp;S Daily Cool Libra</t>
-  </si>
-  <si>
-    <t>CI609: H&amp;S Daily Cool Libra</t>
-  </si>
-  <si>
-    <t>CI604: PTN SS Conditioner</t>
+    <t>CI621: H&amp;S Daily Cool Libra</t>
+  </si>
+  <si>
+    <t>CI622: H&amp;S Daily Cool Libra</t>
+  </si>
+  <si>
+    <t>CI617: PTN SS Conditioner</t>
   </si>
   <si>
     <t>COND WASH (60m)</t>
   </si>
   <si>
-    <t>CI605: H&amp;S Anti dandruff  7in1</t>
-  </si>
-  <si>
-    <t>CI607: H&amp;S Neem Libra</t>
-  </si>
-  <si>
-    <t>TK#_1_#</t>
+    <t>CI618: H&amp;S Anti dandruff  7in1</t>
+  </si>
+  <si>
+    <t>CI620: H&amp;S Neem Libra</t>
   </si>
   <si>
     <t>TK#_5_#</t>
   </si>
   <si>
-    <t>TK#_13_#</t>
-  </si>
-  <si>
-    <t>TK#_22_#</t>
+    <t>TK#_7_#</t>
+  </si>
+  <si>
+    <t>TK#_11_#</t>
+  </si>
+  <si>
+    <t>TK#_16_#</t>
+  </si>
+  <si>
+    <t>TK#_17_#</t>
+  </si>
+  <si>
+    <t>TK#_20_#</t>
   </si>
   <si>
     <t>TK#_24_#</t>
   </si>
   <si>
-    <t>TK#_26_#</t>
-  </si>
-  <si>
     <t>2026-01-20 14:30</t>
   </si>
   <si>
@@ -691,10 +694,10 @@
     <t>2026-01-20 21:00</t>
   </si>
   <si>
+    <t>CI621: H&amp;S Daily Cool Libra | CI622: H&amp;S Daily Cool Libra</t>
+  </si>
+  <si>
     <t>WASHOUT (20m)</t>
-  </si>
-  <si>
-    <t>CI608: H&amp;S Daily Cool Libra | CI609: H&amp;S Daily Cool Libra</t>
   </si>
   <si>
     <t>Sr.No</t>
@@ -1493,19 +1496,19 @@
         <v>51</v>
       </c>
       <c r="K7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L7" s="2">
-        <v>46040.38888888889</v>
+        <v>46040.90069444444</v>
       </c>
       <c r="M7">
         <v>90</v>
       </c>
       <c r="N7" s="2">
-        <v>46040.45138888889</v>
+        <v>46040.96319444444</v>
       </c>
       <c r="O7">
-        <v>2177</v>
+        <v>1440</v>
       </c>
       <c r="P7" t="s">
         <v>59</v>
@@ -1786,9 +1789,6 @@
       <c r="B27" t="s">
         <v>53</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>203</v>
-      </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
@@ -1797,9 +1797,6 @@
       <c r="B28" t="s">
         <v>53</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>203</v>
-      </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
@@ -1808,9 +1805,6 @@
       <c r="B29" t="s">
         <v>53</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>203</v>
-      </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
@@ -1964,7 +1958,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:4">
       <c r="A49" t="s">
         <v>111</v>
       </c>
@@ -1972,7 +1966,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:4">
       <c r="A50" t="s">
         <v>112</v>
       </c>
@@ -1980,7 +1974,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:4">
       <c r="A51" t="s">
         <v>113</v>
       </c>
@@ -1988,31 +1982,40 @@
         <v>54</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:4">
       <c r="A52" t="s">
         <v>114</v>
       </c>
       <c r="B52" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="53" spans="1:2">
+      <c r="D52" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
       <c r="A53" t="s">
         <v>115</v>
       </c>
       <c r="B53" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="54" spans="1:2">
+      <c r="D53" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
       <c r="A54" t="s">
         <v>116</v>
       </c>
       <c r="B54" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="55" spans="1:2">
+      <c r="D54" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
       <c r="A55" t="s">
         <v>117</v>
       </c>
@@ -2020,7 +2023,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:4">
       <c r="A56" t="s">
         <v>118</v>
       </c>
@@ -2028,7 +2031,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:4">
       <c r="A57" t="s">
         <v>119</v>
       </c>
@@ -2036,7 +2039,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:4">
       <c r="A58" t="s">
         <v>120</v>
       </c>
@@ -2044,7 +2047,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:4">
       <c r="A59" t="s">
         <v>121</v>
       </c>
@@ -2052,7 +2055,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:4">
       <c r="A60" t="s">
         <v>122</v>
       </c>
@@ -2060,7 +2063,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:4">
       <c r="A61" t="s">
         <v>123</v>
       </c>
@@ -2068,7 +2071,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:4">
       <c r="A62" t="s">
         <v>124</v>
       </c>
@@ -2076,7 +2079,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:4">
       <c r="A63" t="s">
         <v>125</v>
       </c>
@@ -2084,7 +2087,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:4">
       <c r="A64" t="s">
         <v>126</v>
       </c>
@@ -2695,19 +2698,19 @@
         <v>205</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>58</v>
+        <v>206</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2725,7 +2728,7 @@
       <c r="B3" t="s">
         <v>54</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>200</v>
       </c>
     </row>
@@ -2736,7 +2739,7 @@
       <c r="B4" t="s">
         <v>54</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>200</v>
       </c>
     </row>
@@ -2747,7 +2750,7 @@
       <c r="B5" t="s">
         <v>195</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>200</v>
       </c>
     </row>
@@ -2758,7 +2761,7 @@
       <c r="B6" t="s">
         <v>195</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>200</v>
       </c>
     </row>
@@ -2769,7 +2772,7 @@
       <c r="B7" t="s">
         <v>195</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>200</v>
       </c>
     </row>
@@ -2780,7 +2783,7 @@
       <c r="B8" t="s">
         <v>195</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>200</v>
       </c>
     </row>
@@ -2791,7 +2794,7 @@
       <c r="B9" t="s">
         <v>195</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>200</v>
       </c>
     </row>
@@ -2802,7 +2805,7 @@
       <c r="B10" t="s">
         <v>195</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="E10" s="3" t="s">
         <v>200</v>
       </c>
     </row>
@@ -2813,7 +2816,7 @@
       <c r="B11" t="s">
         <v>195</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="E11" s="3" t="s">
         <v>200</v>
       </c>
     </row>
@@ -2824,7 +2827,7 @@
       <c r="B12" t="s">
         <v>195</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>200</v>
       </c>
     </row>
@@ -2835,7 +2838,7 @@
       <c r="B13" t="s">
         <v>195</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="E13" s="3" t="s">
         <v>200</v>
       </c>
     </row>
@@ -2846,7 +2849,7 @@
       <c r="B14" t="s">
         <v>195</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>200</v>
       </c>
     </row>
@@ -2857,7 +2860,7 @@
       <c r="B15" t="s">
         <v>195</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>200</v>
       </c>
     </row>
@@ -2868,500 +2871,434 @@
       <c r="B16" t="s">
         <v>195</v>
       </c>
-      <c r="I16" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
+      <c r="E16" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>81</v>
       </c>
       <c r="B17" t="s">
         <v>195</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
+      <c r="E17" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>82</v>
       </c>
       <c r="B18" t="s">
         <v>195</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
+      <c r="E18" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>83</v>
       </c>
       <c r="B19" t="s">
         <v>195</v>
       </c>
-      <c r="I19" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
+      <c r="E19" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>84</v>
       </c>
       <c r="B20" t="s">
         <v>195</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
+      <c r="E20" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>85</v>
       </c>
       <c r="B21" t="s">
         <v>53</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
+      <c r="E21" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
         <v>86</v>
       </c>
       <c r="B22" t="s">
         <v>53</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
+      <c r="E22" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
         <v>87</v>
       </c>
       <c r="B23" t="s">
         <v>53</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
+      <c r="E23" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
         <v>88</v>
       </c>
       <c r="B24" t="s">
         <v>53</v>
       </c>
+      <c r="D24" s="3" t="s">
+        <v>202</v>
+      </c>
       <c r="E24" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
         <v>89</v>
       </c>
       <c r="B25" t="s">
         <v>53</v>
       </c>
+      <c r="D25" s="3" t="s">
+        <v>202</v>
+      </c>
       <c r="E25" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" t="s">
         <v>90</v>
       </c>
       <c r="B26" t="s">
         <v>53</v>
       </c>
+      <c r="D26" s="3" t="s">
+        <v>202</v>
+      </c>
       <c r="E26" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
         <v>91</v>
       </c>
       <c r="B27" t="s">
         <v>53</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>224</v>
+      <c r="D27" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" t="s">
         <v>92</v>
       </c>
       <c r="B28" t="s">
         <v>53</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>203</v>
+      <c r="D28" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" t="s">
         <v>93</v>
       </c>
       <c r="B29" t="s">
         <v>53</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>203</v>
+      <c r="D29" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" t="s">
         <v>94</v>
       </c>
       <c r="B30" t="s">
         <v>53</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>203</v>
+      <c r="D30" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31" t="s">
         <v>95</v>
       </c>
       <c r="B31" t="s">
         <v>53</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>203</v>
+      <c r="D31" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" t="s">
         <v>96</v>
       </c>
       <c r="B32" t="s">
         <v>53</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>203</v>
+      <c r="D32" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33" t="s">
         <v>97</v>
       </c>
       <c r="B33" t="s">
         <v>53</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>203</v>
+      <c r="D33" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34" t="s">
         <v>98</v>
       </c>
       <c r="B34" t="s">
         <v>53</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>203</v>
+      <c r="D34" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35" t="s">
         <v>99</v>
       </c>
       <c r="B35" t="s">
         <v>53</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>203</v>
+      <c r="D35" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36" t="s">
         <v>100</v>
       </c>
       <c r="B36" t="s">
         <v>53</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>203</v>
+      <c r="D36" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37" t="s">
         <v>101</v>
       </c>
       <c r="B37" t="s">
         <v>54</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>203</v>
+      <c r="D37" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38" t="s">
         <v>102</v>
       </c>
       <c r="B38" t="s">
         <v>54</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>203</v>
+      <c r="D38" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39" t="s">
         <v>103</v>
       </c>
       <c r="B39" t="s">
         <v>54</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>203</v>
+      <c r="D39" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
       <c r="A40" t="s">
         <v>104</v>
       </c>
       <c r="B40" t="s">
         <v>54</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>203</v>
+      <c r="D40" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
       <c r="A41" t="s">
         <v>105</v>
       </c>
       <c r="B41" t="s">
         <v>54</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>203</v>
+      <c r="D41" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
       <c r="A42" t="s">
         <v>106</v>
       </c>
       <c r="B42" t="s">
         <v>54</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>203</v>
+      <c r="D42" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
       <c r="A43" t="s">
         <v>107</v>
       </c>
       <c r="B43" t="s">
         <v>54</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>203</v>
+      <c r="D43" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
       <c r="A44" t="s">
         <v>108</v>
       </c>
       <c r="B44" t="s">
         <v>54</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>203</v>
+      <c r="D44" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
       <c r="A45" t="s">
         <v>109</v>
       </c>
       <c r="B45" t="s">
         <v>54</v>
       </c>
-      <c r="C45" s="3" t="s">
-        <v>203</v>
+      <c r="D45" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
       <c r="A46" t="s">
         <v>110</v>
       </c>
       <c r="B46" t="s">
         <v>54</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>203</v>
+      <c r="D46" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
       <c r="A47" t="s">
         <v>111</v>
       </c>
       <c r="B47" t="s">
         <v>54</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>203</v>
+      <c r="D47" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
       <c r="A48" t="s">
         <v>112</v>
       </c>
       <c r="B48" t="s">
         <v>54</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>203</v>
+      <c r="D48" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="I48" s="3" t="s">
         <v>200</v>
       </c>
     </row>
@@ -3372,13 +3309,10 @@
       <c r="B49" t="s">
         <v>54</v>
       </c>
-      <c r="C49" s="3" t="s">
-        <v>203</v>
+      <c r="D49" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="I49" s="3" t="s">
         <v>200</v>
       </c>
     </row>
@@ -3389,13 +3323,10 @@
       <c r="B50" t="s">
         <v>54</v>
       </c>
-      <c r="C50" s="3" t="s">
-        <v>203</v>
+      <c r="D50" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="I50" s="3" t="s">
         <v>200</v>
       </c>
     </row>
@@ -3406,13 +3337,10 @@
       <c r="B51" t="s">
         <v>54</v>
       </c>
-      <c r="C51" s="3" t="s">
-        <v>203</v>
+      <c r="D51" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="I51" s="3" t="s">
         <v>200</v>
       </c>
     </row>
@@ -3423,14 +3351,14 @@
       <c r="B52" t="s">
         <v>54</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>203</v>
+      <c r="D52" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -3440,14 +3368,14 @@
       <c r="B53" t="s">
         <v>195</v>
       </c>
-      <c r="C53" s="3" t="s">
-        <v>203</v>
+      <c r="D53" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -3457,14 +3385,14 @@
       <c r="B54" t="s">
         <v>195</v>
       </c>
-      <c r="C54" s="3" t="s">
-        <v>203</v>
+      <c r="D54" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -3474,14 +3402,14 @@
       <c r="B55" t="s">
         <v>195</v>
       </c>
-      <c r="C55" s="3" t="s">
-        <v>203</v>
+      <c r="D55" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -3491,14 +3419,14 @@
       <c r="B56" t="s">
         <v>195</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>203</v>
+      <c r="D56" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -3508,14 +3436,14 @@
       <c r="B57" t="s">
         <v>195</v>
       </c>
-      <c r="C57" s="3" t="s">
-        <v>203</v>
+      <c r="D57" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -3525,14 +3453,14 @@
       <c r="B58" t="s">
         <v>195</v>
       </c>
-      <c r="C58" s="3" t="s">
-        <v>203</v>
+      <c r="D58" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -3542,14 +3470,14 @@
       <c r="B59" t="s">
         <v>195</v>
       </c>
-      <c r="C59" s="3" t="s">
-        <v>203</v>
+      <c r="D59" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -3559,14 +3487,14 @@
       <c r="B60" t="s">
         <v>195</v>
       </c>
-      <c r="C60" s="3" t="s">
-        <v>203</v>
+      <c r="D60" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -3576,14 +3504,14 @@
       <c r="B61" t="s">
         <v>195</v>
       </c>
-      <c r="C61" s="3" t="s">
-        <v>203</v>
+      <c r="D61" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -3593,14 +3521,14 @@
       <c r="B62" t="s">
         <v>195</v>
       </c>
-      <c r="C62" s="3" t="s">
-        <v>203</v>
+      <c r="D62" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -3610,14 +3538,14 @@
       <c r="B63" t="s">
         <v>195</v>
       </c>
-      <c r="C63" s="3" t="s">
-        <v>203</v>
+      <c r="D63" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -3627,14 +3555,14 @@
       <c r="B64" t="s">
         <v>195</v>
       </c>
-      <c r="C64" s="3" t="s">
-        <v>203</v>
+      <c r="D64" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -3644,14 +3572,14 @@
       <c r="B65" t="s">
         <v>195</v>
       </c>
-      <c r="C65" s="3" t="s">
-        <v>203</v>
+      <c r="D65" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -3661,14 +3589,14 @@
       <c r="B66" t="s">
         <v>195</v>
       </c>
-      <c r="C66" s="3" t="s">
-        <v>203</v>
+      <c r="D66" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -3678,14 +3606,14 @@
       <c r="B67" t="s">
         <v>195</v>
       </c>
-      <c r="C67" s="3" t="s">
-        <v>203</v>
+      <c r="D67" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -3695,14 +3623,14 @@
       <c r="B68" t="s">
         <v>195</v>
       </c>
-      <c r="C68" s="3" t="s">
-        <v>203</v>
+      <c r="D68" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -3712,14 +3640,14 @@
       <c r="B69" t="s">
         <v>53</v>
       </c>
-      <c r="C69" s="3" t="s">
-        <v>203</v>
+      <c r="D69" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -3729,14 +3657,14 @@
       <c r="B70" t="s">
         <v>53</v>
       </c>
-      <c r="C70" s="3" t="s">
-        <v>203</v>
+      <c r="D70" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -3746,14 +3674,14 @@
       <c r="B71" t="s">
         <v>53</v>
       </c>
-      <c r="C71" s="3" t="s">
-        <v>203</v>
+      <c r="D71" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -3763,14 +3691,14 @@
       <c r="B72" t="s">
         <v>53</v>
       </c>
-      <c r="C72" s="3" t="s">
-        <v>203</v>
+      <c r="D72" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -3780,14 +3708,14 @@
       <c r="B73" t="s">
         <v>53</v>
       </c>
-      <c r="C73" s="3" t="s">
-        <v>203</v>
+      <c r="D73" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -3797,14 +3725,14 @@
       <c r="B74" t="s">
         <v>53</v>
       </c>
-      <c r="C74" s="3" t="s">
-        <v>203</v>
+      <c r="D74" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -3814,14 +3742,14 @@
       <c r="B75" t="s">
         <v>53</v>
       </c>
-      <c r="C75" s="3" t="s">
-        <v>203</v>
+      <c r="D75" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -3831,14 +3759,14 @@
       <c r="B76" t="s">
         <v>53</v>
       </c>
-      <c r="C76" s="3" t="s">
-        <v>203</v>
+      <c r="D76" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -3848,14 +3776,14 @@
       <c r="B77" t="s">
         <v>53</v>
       </c>
-      <c r="C77" s="3" t="s">
-        <v>203</v>
+      <c r="D77" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -3865,11 +3793,11 @@
       <c r="B78" t="s">
         <v>53</v>
       </c>
-      <c r="C78" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>202</v>
+      <c r="D78" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -3879,11 +3807,11 @@
       <c r="B79" t="s">
         <v>53</v>
       </c>
-      <c r="C79" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>202</v>
+      <c r="D79" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -3893,84 +3821,84 @@
       <c r="B80" t="s">
         <v>53</v>
       </c>
-      <c r="C80" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8">
+      <c r="D80" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
       <c r="A81" t="s">
         <v>145</v>
       </c>
       <c r="B81" t="s">
         <v>53</v>
       </c>
-      <c r="C81" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8">
+      <c r="D81" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
       <c r="A82" t="s">
         <v>146</v>
       </c>
       <c r="B82" t="s">
         <v>53</v>
       </c>
-      <c r="C82" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8">
+      <c r="D82" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
       <c r="A83" t="s">
         <v>147</v>
       </c>
       <c r="B83" t="s">
         <v>53</v>
       </c>
-      <c r="C83" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8">
+      <c r="D83" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
       <c r="A84" t="s">
         <v>148</v>
       </c>
       <c r="B84" t="s">
         <v>53</v>
       </c>
-      <c r="C84" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E84" s="3" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8">
+      <c r="D84" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
       <c r="A85" t="s">
         <v>149</v>
       </c>
       <c r="B85" t="s">
         <v>54</v>
       </c>
-      <c r="C85" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8">
+      <c r="D85" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
       <c r="A86" t="s">
         <v>150</v>
       </c>
@@ -3978,19 +3906,19 @@
         <v>54</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E86" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D86" s="3" t="s">
         <v>202</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="H86" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8">
+      <c r="I86" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
       <c r="A87" t="s">
         <v>151</v>
       </c>
@@ -3998,19 +3926,19 @@
         <v>54</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E87" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D87" s="3" t="s">
         <v>202</v>
       </c>
       <c r="G87" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="H87" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8">
+      <c r="I87" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
       <c r="A88" t="s">
         <v>152</v>
       </c>
@@ -4018,19 +3946,19 @@
         <v>54</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E88" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D88" s="3" t="s">
         <v>202</v>
       </c>
       <c r="G88" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="H88" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8">
+      <c r="I88" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9">
       <c r="A89" t="s">
         <v>153</v>
       </c>
@@ -4038,19 +3966,19 @@
         <v>54</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E89" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D89" s="3" t="s">
         <v>202</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8">
+      <c r="I89" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9">
       <c r="A90" t="s">
         <v>154</v>
       </c>
@@ -4058,19 +3986,19 @@
         <v>54</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E90" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D90" s="3" t="s">
         <v>202</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="H90" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8">
+      <c r="I90" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9">
       <c r="A91" t="s">
         <v>155</v>
       </c>
@@ -4078,19 +4006,19 @@
         <v>54</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E91" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D91" s="3" t="s">
         <v>202</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8">
+      <c r="I91" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9">
       <c r="A92" t="s">
         <v>156</v>
       </c>
@@ -4098,19 +4026,19 @@
         <v>54</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E92" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D92" s="3" t="s">
         <v>202</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="H92" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8">
+      <c r="I92" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
       <c r="A93" t="s">
         <v>157</v>
       </c>
@@ -4118,19 +4046,19 @@
         <v>54</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E93" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D93" s="3" t="s">
         <v>202</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="H93" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8">
+      <c r="I93" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
       <c r="A94" t="s">
         <v>158</v>
       </c>
@@ -4138,19 +4066,19 @@
         <v>54</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E94" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D94" s="3" t="s">
         <v>202</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8">
+      <c r="I94" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9">
       <c r="A95" t="s">
         <v>159</v>
       </c>
@@ -4158,19 +4086,19 @@
         <v>54</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E95" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D95" s="3" t="s">
         <v>202</v>
       </c>
       <c r="G95" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="H95" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8">
+      <c r="I95" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
       <c r="A96" t="s">
         <v>160</v>
       </c>
@@ -4178,19 +4106,19 @@
         <v>54</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E96" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D96" s="3" t="s">
         <v>202</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8">
+      <c r="I96" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9">
       <c r="A97" t="s">
         <v>161</v>
       </c>
@@ -4198,19 +4126,19 @@
         <v>54</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E97" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D97" s="3" t="s">
         <v>202</v>
       </c>
       <c r="G97" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="H97" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8">
+      <c r="I97" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
       <c r="A98" t="s">
         <v>162</v>
       </c>
@@ -4218,19 +4146,19 @@
         <v>54</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E98" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D98" s="3" t="s">
         <v>202</v>
       </c>
       <c r="G98" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="H98" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8">
+      <c r="I98" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
       <c r="A99" t="s">
         <v>163</v>
       </c>
@@ -4238,19 +4166,19 @@
         <v>54</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E99" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D99" s="3" t="s">
         <v>202</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="H99" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8">
+      <c r="I99" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
       <c r="A100" t="s">
         <v>164</v>
       </c>
@@ -4258,731 +4186,731 @@
         <v>54</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E100" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D100" s="3" t="s">
         <v>202</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8">
+      <c r="I100" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9">
       <c r="A101" t="s">
         <v>165</v>
       </c>
       <c r="B101" t="s">
         <v>195</v>
       </c>
-      <c r="C101" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="D101" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E101" s="3" t="s">
         <v>202</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="102" spans="1:8">
+      <c r="H101" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9">
       <c r="A102" t="s">
         <v>166</v>
       </c>
       <c r="B102" t="s">
         <v>195</v>
       </c>
-      <c r="C102" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="D102" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E102" s="3" t="s">
         <v>202</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="103" spans="1:8">
+      <c r="H102" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
       <c r="A103" t="s">
         <v>167</v>
       </c>
       <c r="B103" t="s">
         <v>195</v>
       </c>
-      <c r="C103" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="D103" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E103" s="3" t="s">
         <v>202</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="104" spans="1:8">
+      <c r="H103" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="I103" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9">
       <c r="A104" t="s">
         <v>168</v>
       </c>
       <c r="B104" t="s">
         <v>195</v>
       </c>
-      <c r="C104" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="D104" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E104" s="3" t="s">
         <v>202</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="105" spans="1:8">
+      <c r="H104" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="I104" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9">
       <c r="A105" t="s">
         <v>169</v>
       </c>
       <c r="B105" t="s">
         <v>195</v>
       </c>
-      <c r="C105" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="D105" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E105" s="3" t="s">
         <v>202</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="106" spans="1:8">
+      <c r="H105" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="I105" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9">
       <c r="A106" t="s">
         <v>170</v>
       </c>
       <c r="B106" t="s">
         <v>195</v>
       </c>
-      <c r="C106" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="D106" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E106" s="3" t="s">
         <v>202</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="107" spans="1:8">
+      <c r="H106" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="I106" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9">
       <c r="A107" t="s">
         <v>171</v>
       </c>
       <c r="B107" t="s">
         <v>195</v>
       </c>
-      <c r="C107" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="D107" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E107" s="3" t="s">
         <v>202</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="108" spans="1:8">
+      <c r="H107" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="I107" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9">
       <c r="A108" t="s">
         <v>172</v>
       </c>
       <c r="B108" t="s">
         <v>195</v>
       </c>
-      <c r="C108" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="D108" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E108" s="3" t="s">
         <v>202</v>
       </c>
       <c r="F108" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="109" spans="1:8">
+      <c r="H108" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="I108" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9">
       <c r="A109" t="s">
         <v>173</v>
       </c>
       <c r="B109" t="s">
         <v>195</v>
       </c>
-      <c r="C109" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="D109" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E109" s="3" t="s">
         <v>202</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="110" spans="1:8">
+      <c r="H109" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="I109" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9">
       <c r="A110" t="s">
         <v>174</v>
       </c>
       <c r="B110" t="s">
         <v>195</v>
       </c>
-      <c r="C110" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="D110" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E110" s="3" t="s">
         <v>202</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="111" spans="1:8">
+      <c r="H110" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="I110" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9">
       <c r="A111" t="s">
         <v>175</v>
       </c>
       <c r="B111" t="s">
         <v>195</v>
       </c>
-      <c r="C111" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="D111" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E111" s="3" t="s">
         <v>202</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="112" spans="1:8">
+      <c r="H111" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="I111" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9">
       <c r="A112" t="s">
         <v>176</v>
       </c>
       <c r="B112" t="s">
         <v>195</v>
       </c>
-      <c r="C112" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="D112" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E112" s="3" t="s">
         <v>202</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="113" spans="1:6">
+      <c r="H112" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9">
       <c r="A113" t="s">
         <v>177</v>
       </c>
       <c r="B113" t="s">
         <v>195</v>
       </c>
-      <c r="C113" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="D113" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E113" s="3" t="s">
         <v>202</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="114" spans="1:6">
+      <c r="H113" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="I113" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9">
       <c r="A114" t="s">
         <v>178</v>
       </c>
       <c r="B114" t="s">
         <v>195</v>
       </c>
-      <c r="C114" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="D114" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E114" s="3" t="s">
         <v>202</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="115" spans="1:6">
+      <c r="H114" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="I114" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9">
       <c r="A115" t="s">
         <v>179</v>
       </c>
       <c r="B115" t="s">
         <v>195</v>
       </c>
-      <c r="C115" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="D115" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E115" s="3" t="s">
         <v>202</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="116" spans="1:6">
+      <c r="H115" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="I115" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9">
       <c r="A116" t="s">
         <v>180</v>
       </c>
       <c r="B116" t="s">
         <v>195</v>
       </c>
-      <c r="C116" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="D116" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E116" s="3" t="s">
         <v>202</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="117" spans="1:6">
+      <c r="H116" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="I116" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9">
       <c r="A117" t="s">
         <v>181</v>
       </c>
       <c r="B117" t="s">
         <v>53</v>
       </c>
-      <c r="C117" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="D117" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E117" s="3" t="s">
         <v>202</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="118" spans="1:6">
+      <c r="H117" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="I117" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9">
       <c r="A118" t="s">
         <v>182</v>
       </c>
       <c r="B118" t="s">
         <v>53</v>
       </c>
-      <c r="C118" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="D118" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E118" s="3" t="s">
         <v>202</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="119" spans="1:6">
+      <c r="H118" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="I118" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9">
       <c r="A119" t="s">
         <v>183</v>
       </c>
       <c r="B119" t="s">
         <v>53</v>
       </c>
-      <c r="C119" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="D119" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E119" s="3" t="s">
         <v>202</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="120" spans="1:6">
+      <c r="H119" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="I119" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9">
       <c r="A120" t="s">
         <v>184</v>
       </c>
       <c r="B120" t="s">
         <v>53</v>
       </c>
-      <c r="C120" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D120" s="3" t="s">
-        <v>198</v>
-      </c>
       <c r="F120" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="121" spans="1:6">
+      <c r="H120" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="I120" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9">
       <c r="A121" t="s">
         <v>185</v>
       </c>
       <c r="B121" t="s">
         <v>53</v>
       </c>
-      <c r="C121" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D121" s="3" t="s">
-        <v>198</v>
-      </c>
       <c r="F121" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="122" spans="1:6">
+      <c r="H121" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="I121" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9">
       <c r="A122" t="s">
         <v>186</v>
       </c>
       <c r="B122" t="s">
         <v>53</v>
       </c>
-      <c r="D122" s="3" t="s">
-        <v>198</v>
-      </c>
       <c r="F122" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="123" spans="1:6">
+      <c r="H122" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9">
       <c r="A123" t="s">
         <v>187</v>
       </c>
       <c r="B123" t="s">
         <v>53</v>
       </c>
-      <c r="D123" s="3" t="s">
-        <v>198</v>
-      </c>
       <c r="F123" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="124" spans="1:6">
+      <c r="H123" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9">
       <c r="A124" t="s">
         <v>188</v>
       </c>
       <c r="B124" t="s">
         <v>53</v>
       </c>
-      <c r="D124" s="3" t="s">
-        <v>198</v>
-      </c>
       <c r="F124" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="125" spans="1:6">
+      <c r="H124" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9">
       <c r="A125" t="s">
         <v>189</v>
       </c>
       <c r="B125" t="s">
         <v>53</v>
       </c>
-      <c r="D125" s="3" t="s">
-        <v>198</v>
-      </c>
       <c r="F125" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="126" spans="1:6">
+      <c r="H125" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9">
       <c r="A126" t="s">
         <v>190</v>
       </c>
       <c r="B126" t="s">
         <v>53</v>
       </c>
-      <c r="D126" s="3" t="s">
-        <v>198</v>
-      </c>
       <c r="F126" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="127" spans="1:6">
+      <c r="H126" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9">
       <c r="A127" t="s">
         <v>191</v>
       </c>
       <c r="B127" t="s">
         <v>53</v>
       </c>
-      <c r="D127" s="3" t="s">
-        <v>198</v>
-      </c>
       <c r="F127" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="128" spans="1:6">
+      <c r="H127" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9">
       <c r="A128" t="s">
         <v>192</v>
       </c>
       <c r="B128" t="s">
         <v>53</v>
       </c>
-      <c r="D128" s="3" t="s">
-        <v>225</v>
-      </c>
       <c r="F128" s="3" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="129" spans="1:6">
+      <c r="H128" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8">
       <c r="A129" t="s">
         <v>193</v>
       </c>
       <c r="B129" t="s">
         <v>53</v>
       </c>
-      <c r="D129" s="3" t="s">
-        <v>225</v>
-      </c>
       <c r="F129" s="3" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="130" spans="1:6">
+      <c r="H129" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8">
       <c r="A130" t="s">
         <v>194</v>
       </c>
       <c r="B130" t="s">
         <v>53</v>
       </c>
-      <c r="D130" s="3" t="s">
-        <v>225</v>
-      </c>
       <c r="F130" s="3" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="131" spans="1:6">
+      <c r="H130" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
       <c r="A131" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B131" t="s">
         <v>53</v>
-      </c>
-      <c r="D131" s="3" t="s">
-        <v>225</v>
       </c>
       <c r="F131" s="3" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="132" spans="1:6">
+      <c r="H131" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8">
       <c r="A132" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B132" t="s">
         <v>53</v>
-      </c>
-      <c r="D132" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="133" spans="1:6">
+      <c r="H132" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8">
       <c r="A133" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B133" t="s">
         <v>54</v>
-      </c>
-      <c r="D133" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="134" spans="1:6">
+      <c r="H133" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8">
       <c r="A134" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B134" t="s">
         <v>54</v>
-      </c>
-      <c r="D134" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="F134" s="3" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="135" spans="1:6">
+      <c r="H134" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8">
       <c r="A135" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B135" t="s">
         <v>54</v>
-      </c>
-      <c r="D135" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="F135" s="3" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="136" spans="1:6">
+      <c r="H135" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8">
       <c r="A136" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B136" t="s">
         <v>54</v>
-      </c>
-      <c r="D136" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="F136" s="3" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="137" spans="1:6">
+      <c r="H136" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8">
       <c r="A137" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B137" t="s">
         <v>54</v>
-      </c>
-      <c r="D137" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="F137" s="3" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="138" spans="1:6">
+      <c r="H137" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8">
       <c r="A138" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B138" t="s">
         <v>54</v>
-      </c>
-      <c r="D138" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="139" spans="1:6">
+      <c r="H138" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8">
       <c r="A139" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B139" t="s">
         <v>54</v>
-      </c>
-      <c r="D139" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="140" spans="1:6">
+      <c r="H139" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8">
       <c r="A140" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B140" t="s">
         <v>54</v>
-      </c>
-      <c r="D140" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="F140" s="3" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="141" spans="1:6">
+      <c r="H140" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8">
       <c r="A141" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B141" t="s">
         <v>54</v>
-      </c>
-      <c r="D141" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="F141" s="3" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="142" spans="1:6">
+      <c r="H141" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8">
       <c r="A142" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B142" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:8">
       <c r="A143" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B143" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:8">
       <c r="A144" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B144" t="s">
         <v>54</v>
@@ -5005,34 +4933,34 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -5040,7 +4968,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C2" t="s">
         <v>37</v>
@@ -5066,7 +4994,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C3" t="s">
         <v>38</v>
@@ -5092,7 +5020,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C4" t="s">
         <v>39</v>
@@ -5118,7 +5046,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C5" t="s">
         <v>40</v>
@@ -5144,7 +5072,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C6" t="s">
         <v>41</v>
@@ -5170,7 +5098,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C7" t="s">
         <v>42</v>
